--- a/templates/BNY12578 - template.xlsx
+++ b/templates/BNY12578 - template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="711" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="20355" yWindow="-11640" windowWidth="20730" windowHeight="11040" tabRatio="711" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Email" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Email" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="DataAnálise">Email!$A$7</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Email'!$B$7:$F$43</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Email'!$B$7:$F$44</definedName>
   </definedNames>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
@@ -1261,8 +1261,8 @@
     <col width="5.42578125" customWidth="1" style="2" min="7" max="7"/>
     <col width="23.140625" bestFit="1" customWidth="1" style="2" min="8" max="8"/>
     <col width="23.42578125" bestFit="1" customWidth="1" style="2" min="9" max="9"/>
-    <col width="9.140625" customWidth="1" style="2" min="10" max="17"/>
-    <col width="9.140625" customWidth="1" style="2" min="18" max="16384"/>
+    <col width="9.140625" customWidth="1" style="2" min="10" max="18"/>
+    <col width="9.140625" customWidth="1" style="2" min="19" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" hidden="1">
@@ -1414,96 +1414,96 @@
     <row r="18" ht="15.95" customFormat="1" customHeight="1" s="35">
       <c r="B18" s="36" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C18" s="37" t="n">
-        <v>0.81815396</v>
+        <v>0.82689849</v>
       </c>
       <c r="D18" s="38" t="n">
-        <v>0.0008441963415972698</v>
+        <v>0.0007830061143729861</v>
       </c>
       <c r="E18" s="38" t="n">
         <v>0.0005426623598601132</v>
       </c>
       <c r="F18" s="39" t="n">
-        <v>1.555656710398867</v>
+        <v>1.442897411522753</v>
       </c>
     </row>
     <row r="19" ht="15.95" customFormat="1" customHeight="1" s="35">
       <c r="B19" s="40" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="C19" s="41" t="n">
-        <v>0.81746386</v>
+        <v>0.82625153</v>
       </c>
       <c r="D19" s="42" t="n">
-        <v>0.0009484390440390733</v>
+        <v>0.0007944203582659348</v>
       </c>
       <c r="E19" s="42" t="n">
         <v>0.0005426623598601132</v>
       </c>
       <c r="F19" s="43" t="n">
-        <v>1.74775166695468</v>
+        <v>1.463931197422131</v>
       </c>
     </row>
     <row r="20" ht="15.95" customFormat="1" customHeight="1" s="35">
       <c r="B20" s="40" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="C20" s="41" t="n">
-        <v>0.81668928</v>
+        <v>0.82559566</v>
       </c>
       <c r="D20" s="42" t="n">
-        <v>0.000849035535656073</v>
+        <v>0.0008405601691390263</v>
       </c>
       <c r="E20" s="42" t="n">
         <v>0.0005426623598601132</v>
       </c>
       <c r="F20" s="43" t="n">
-        <v>1.564574214940827</v>
+        <v>1.548956093722264</v>
       </c>
     </row>
     <row r="21" ht="15.95" customFormat="1" customHeight="1" s="35">
       <c r="B21" s="40" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="C21" s="41" t="n">
-        <v>0.81599647</v>
+        <v>0.82490228</v>
       </c>
       <c r="D21" s="42" t="n">
-        <v>0.001037476784816027</v>
+        <v>0.0006803248741122925</v>
       </c>
       <c r="E21" s="42" t="n">
         <v>0.0005426623598601132</v>
       </c>
       <c r="F21" s="43" t="n">
-        <v>1.911827430012773</v>
+        <v>1.253679865114775</v>
       </c>
     </row>
     <row r="22" ht="15.95" customFormat="1" customHeight="1" s="35">
       <c r="B22" s="40" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="C22" s="41" t="n">
-        <v>0.81515077</v>
+        <v>0.82434146</v>
       </c>
       <c r="D22" s="42" t="n">
-        <v>0.0007895690017207802</v>
+        <v>0.0008153144747025109</v>
       </c>
       <c r="E22" s="42" t="n">
         <v>0.0005426623598601132</v>
       </c>
       <c r="F22" s="43" t="n">
-        <v>1.454991280258159</v>
+        <v>1.502434174562396</v>
       </c>
     </row>
     <row r="23" ht="15.95" customHeight="1">
@@ -1543,18 +1543,18 @@
     <row r="25" ht="15.95" customFormat="1" customHeight="1" s="35">
       <c r="B25" s="44" t="inlineStr">
         <is>
-          <t>Mar-26</t>
+          <t>Apr-26</t>
         </is>
       </c>
       <c r="C25" s="44" t="inlineStr"/>
       <c r="D25" s="38" t="n">
-        <v>-0.01367612239051308</v>
+        <v>0.006571650381738348</v>
       </c>
       <c r="E25" s="38" t="n">
-        <v>0.01048336746569301</v>
+        <v>0.003804826246388782</v>
       </c>
       <c r="F25" s="39" t="n">
-        <v>-1.304554327153791</v>
+        <v>1.727188038606389</v>
       </c>
       <c r="G25" s="45" t="n"/>
     </row>
@@ -1567,13 +1567,13 @@
       </c>
       <c r="C26" s="47" t="inlineStr"/>
       <c r="D26" s="42" t="n">
-        <v>0.0273489347303888</v>
+        <v>0.02048160550471168</v>
       </c>
       <c r="E26" s="42" t="n">
-        <v>0.01159785506263344</v>
+        <v>0.0115104208368324</v>
       </c>
       <c r="F26" s="43" t="n">
-        <v>2.358102820107054</v>
+        <v>1.779396756647873</v>
       </c>
       <c r="G26" s="48" t="n"/>
       <c r="H26" s="49" t="n"/>
@@ -1587,13 +1587,13 @@
       </c>
       <c r="C27" s="47" t="inlineStr"/>
       <c r="D27" s="42" t="n">
-        <v>0.09665767862545627</v>
+        <v>0.1051470114172093</v>
       </c>
       <c r="E27" s="42" t="n">
-        <v>0.03528813776398843</v>
+        <v>0.03519865594435645</v>
       </c>
       <c r="F27" s="43" t="n">
-        <v>2.739098313204147</v>
+        <v>2.987245069341006</v>
       </c>
       <c r="G27" s="48" t="n"/>
     </row>
@@ -1606,13 +1606,13 @@
       </c>
       <c r="C28" s="47" t="inlineStr"/>
       <c r="D28" s="42" t="n">
-        <v>0.1469265440246004</v>
+        <v>0.1557228961381285</v>
       </c>
       <c r="E28" s="42" t="n">
-        <v>0.07186785093087189</v>
+        <v>0.07177520746070365</v>
       </c>
       <c r="F28" s="43" t="n">
-        <v>2.044398741878699</v>
+        <v>2.169591724599132</v>
       </c>
       <c r="G28" s="48" t="n"/>
     </row>
@@ -1625,13 +1625,13 @@
       </c>
       <c r="C29" s="47" t="inlineStr"/>
       <c r="D29" s="42" t="n">
-        <v>0.1610790695773423</v>
+        <v>0.1734311070442309</v>
       </c>
       <c r="E29" s="42" t="n">
-        <v>0.1478169439809287</v>
+        <v>0.148016036262707</v>
       </c>
       <c r="F29" s="43" t="n">
-        <v>1.089719928170918</v>
+        <v>1.17170484646958</v>
       </c>
       <c r="G29" s="48" t="n"/>
     </row>
@@ -1644,13 +1644,13 @@
       </c>
       <c r="C30" s="47" t="inlineStr"/>
       <c r="D30" s="42" t="n">
-        <v>0.09519501725959567</v>
+        <v>0.1069005961023322</v>
       </c>
       <c r="E30" s="42" t="n">
-        <v>0.03243902489712824</v>
+        <v>0.0380553842733744</v>
       </c>
       <c r="F30" s="43" t="n">
-        <v>2.934583192974554</v>
+        <v>2.809079402126168</v>
       </c>
       <c r="G30" s="48" t="n"/>
     </row>
@@ -1701,18 +1701,18 @@
       </c>
       <c r="C33" s="47" t="inlineStr"/>
       <c r="D33" s="42" t="n">
-        <v>-0.18184604</v>
+        <v>-0.17310151</v>
       </c>
       <c r="E33" s="42" t="n">
-        <v>0.2514890962531993</v>
+        <v>0.2582970649085028</v>
       </c>
       <c r="F33" s="43" t="n">
-        <v>-0.7230772336026744</v>
+        <v>-0.6701644482925818</v>
       </c>
       <c r="G33" s="48" t="n"/>
     </row>
-    <row r="34"/>
-    <row r="35" ht="26.1" customHeight="1">
+    <row r="34" ht="15.95" customFormat="1" customHeight="1" s="35"/>
+    <row r="35">
       <c r="A35" s="13" t="n"/>
       <c r="B35" s="32" t="inlineStr">
         <is>
@@ -1725,7 +1725,7 @@
       <c r="F35" s="32" t="n"/>
       <c r="G35" s="4" t="n"/>
     </row>
-    <row r="36" ht="15.95" customHeight="1">
+    <row r="36" ht="26.1" customHeight="1">
       <c r="A36" s="16" t="n"/>
       <c r="B36" s="14" t="inlineStr">
         <is>
@@ -1735,7 +1735,7 @@
       <c r="C36" s="15" t="n"/>
       <c r="D36" s="15" t="n"/>
       <c r="E36" s="51" t="n">
-        <v>6074808.06</v>
+        <v>6139736.34</v>
       </c>
       <c r="F36" s="30" t="n"/>
       <c r="G36" s="4" t="n"/>
@@ -1750,7 +1750,7 @@
       <c r="C37" s="15" t="n"/>
       <c r="D37" s="15" t="n"/>
       <c r="E37" s="51" t="n">
-        <v>4922749.898095238</v>
+        <v>5017335.295277777</v>
       </c>
       <c r="F37" s="30" t="n"/>
       <c r="G37" s="4" t="n"/>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" s="20" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="D39" s="21" t="n"/>
@@ -1805,7 +1805,7 @@
       <c r="F41" s="23" t="n"/>
       <c r="G41" s="4" t="n"/>
     </row>
-    <row r="42" ht="51.75" customHeight="1">
+    <row r="42" ht="15.95" customHeight="1">
       <c r="A42" s="4" t="n"/>
       <c r="B42" s="34" t="inlineStr">
         <is>
@@ -1818,7 +1818,7 @@
       <c r="F42" s="34" t="n"/>
       <c r="G42" s="4" t="n"/>
     </row>
-    <row r="43">
+    <row r="43" ht="51.75" customHeight="1">
       <c r="A43" s="4" t="n"/>
       <c r="B43" s="33" t="n"/>
       <c r="C43" s="33" t="n"/>
@@ -1855,6 +1855,6 @@
   </sheetData>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" paperSize="9" scale="84" fitToHeight="1" fitToWidth="1"/>
+  <pageSetup orientation="landscape" paperSize="9" scale="83"/>
 </worksheet>
 </file>